--- a/Exams/Exam-02/CheckList_MoneyBankService.xlsx
+++ b/Exams/Exam-02/CheckList_MoneyBankService.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Repositories\ServicesDevelopment\Exams\Exam-02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EE23F7-C507-41AC-9175-7D8BEE8F7113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC817C8A-2730-4A20-81BE-C892EA154B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="748" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="54">
   <si>
     <t>Categoria/Detalle</t>
   </si>
@@ -177,6 +177,27 @@
   </si>
   <si>
     <t>2 Warnings</t>
+  </si>
+  <si>
+    <t>No existe la Opcion</t>
+  </si>
+  <si>
+    <t>No s epuede Probrar</t>
+  </si>
+  <si>
+    <t>La Exception no se controla correctamente</t>
+  </si>
+  <si>
+    <t>Actualiza la Cuenta con el Nuevo Numero de Cuenta</t>
+  </si>
+  <si>
+    <t>Falla por el Tipo de Dato del valueAmoun debe ser Decimal</t>
+  </si>
+  <si>
+    <t>Excepcion No se Controla Correctamente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Metodos de Buscar Cuenta por Id y por Numero de Cuenta son Ineficentes, podria haber reutilizado el Find </t>
   </si>
 </sst>
 </file>
@@ -630,10 +651,10 @@
     <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -647,7 +668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>27</v>
       </c>
@@ -658,7 +679,7 @@
       </c>
       <c r="D3" s="6"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -670,7 +691,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -678,7 +699,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="10"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>12</v>
       </c>
@@ -690,7 +711,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>13</v>
       </c>
@@ -702,7 +723,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
@@ -710,7 +731,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="10"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>14</v>
       </c>
@@ -722,7 +743,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>16</v>
       </c>
@@ -734,7 +755,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>17</v>
       </c>
@@ -746,7 +767,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>18</v>
       </c>
@@ -758,7 +779,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>19</v>
       </c>
@@ -770,31 +791,41 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B14" s="4">
         <v>0.1</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D14" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="4">
         <v>0.1</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D15" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>7</v>
       </c>
@@ -806,19 +837,24 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="4">
         <v>0.1</v>
       </c>
-      <c r="C17" s="4"/>
+      <c r="C17" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D17" s="10">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
@@ -826,7 +862,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="10"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>20</v>
       </c>
@@ -838,7 +874,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>21</v>
       </c>
@@ -850,7 +886,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>22</v>
       </c>
@@ -862,19 +898,24 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="4">
         <v>0.1</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D22" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>10</v>
       </c>
@@ -886,31 +927,41 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="4">
         <v>0.1</v>
       </c>
-      <c r="C24" s="4"/>
+      <c r="C24" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D24" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="4">
         <v>0.1</v>
       </c>
-      <c r="C25" s="4"/>
+      <c r="C25" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D25" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>21</v>
       </c>
@@ -922,19 +973,24 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B27" s="4">
         <v>0.1</v>
       </c>
-      <c r="C27" s="4"/>
+      <c r="C27" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D27" s="10">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>23</v>
       </c>
@@ -946,7 +1002,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>11</v>
       </c>
@@ -954,7 +1010,7 @@
       <c r="C29" s="4"/>
       <c r="D29" s="10"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>24</v>
       </c>
@@ -966,7 +1022,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>25</v>
       </c>
@@ -978,7 +1034,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>26</v>
       </c>
@@ -1009,9 +1065,14 @@
       <c r="B34" s="4">
         <v>0.1</v>
       </c>
-      <c r="C34" s="4"/>
+      <c r="C34" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D34" s="10">
         <v>0.1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1181,7 +1242,9 @@
       <c r="B48" s="4">
         <v>0.5</v>
       </c>
-      <c r="C48" s="4"/>
+      <c r="C48" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D48" s="10">
         <v>0.4</v>
       </c>
@@ -1189,19 +1252,24 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
         <v>42</v>
       </c>
       <c r="B49" s="4">
         <v>0.5</v>
       </c>
-      <c r="C49" s="4"/>
+      <c r="C49" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D49" s="10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+      <c r="E49" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>4</v>
       </c>
@@ -1212,7 +1280,7 @@
       </c>
       <c r="D50" s="9">
         <f>SUM(D3:D49)</f>
-        <v>4.700000000000002</v>
+        <v>4.0000000000000018</v>
       </c>
     </row>
   </sheetData>

--- a/Exams/Exam-02/CheckList_MoneyBankService.xlsx
+++ b/Exams/Exam-02/CheckList_MoneyBankService.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulioCesarRoblesUrib\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\Repositories\ServicesDevelopment\Exams\Exam-02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8134937-4447-4B15-A0C0-BD4C64AE9355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C3234A-37A4-4030-B1C2-8DD775A40CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="748" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="52">
   <si>
     <t>Categoria/Detalle</t>
   </si>
@@ -165,6 +165,33 @@
   </si>
   <si>
     <t>Codigo Legible, Entendible y Mantenible</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Incorrecta la Ruta de AccountNumber y de Retiro</t>
+  </si>
+  <si>
+    <t>Incorrecto uso del Dto en capa Domain</t>
+  </si>
+  <si>
+    <t>Incorrecta la Ruta pero Funciona</t>
+  </si>
+  <si>
+    <t>Debe Traer una lista Vacia</t>
+  </si>
+  <si>
+    <t>Sobregiro puede ser Cero</t>
+  </si>
+  <si>
+    <t>Debe retornar NoContent pero funciona</t>
+  </si>
+  <si>
+    <t>No Controla el Error</t>
+  </si>
+  <si>
+    <t>Falla al actualizar el sobregiro</t>
   </si>
 </sst>
 </file>
@@ -609,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="63.109375" bestFit="1" customWidth="1"/>
@@ -618,10 +645,10 @@
     <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -635,7 +662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>27</v>
       </c>
@@ -646,7 +673,7 @@
       </c>
       <c r="D3" s="6"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -658,7 +685,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -666,7 +693,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="10"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>12</v>
       </c>
@@ -678,7 +705,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>13</v>
       </c>
@@ -690,7 +717,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>15</v>
       </c>
@@ -698,7 +725,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="10"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>14</v>
       </c>
@@ -710,7 +737,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>16</v>
       </c>
@@ -722,7 +749,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>17</v>
       </c>
@@ -734,7 +761,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>18</v>
       </c>
@@ -746,7 +773,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>19</v>
       </c>
@@ -758,31 +785,41 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B14" s="4">
         <v>0.1</v>
       </c>
-      <c r="C14" s="4"/>
+      <c r="C14" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D14" s="10">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="4">
         <v>0.1</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D15" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>7</v>
       </c>
@@ -794,7 +831,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>30</v>
       </c>
@@ -806,7 +843,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
@@ -814,7 +851,7 @@
       <c r="C18" s="4"/>
       <c r="D18" s="10"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>20</v>
       </c>
@@ -826,7 +863,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>21</v>
       </c>
@@ -838,7 +875,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>22</v>
       </c>
@@ -850,7 +887,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>23</v>
       </c>
@@ -862,7 +899,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>10</v>
       </c>
@@ -874,43 +911,58 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="4">
         <v>0.1</v>
       </c>
-      <c r="C24" s="4"/>
+      <c r="C24" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D24" s="10">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B25" s="4">
         <v>0.1</v>
       </c>
-      <c r="C25" s="4"/>
+      <c r="C25" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D25" s="10">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>21</v>
       </c>
       <c r="B26" s="4">
         <v>0.1</v>
       </c>
-      <c r="C26" s="4"/>
+      <c r="C26" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D26" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>22</v>
       </c>
@@ -922,7 +974,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>23</v>
       </c>
@@ -934,7 +986,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>11</v>
       </c>
@@ -942,31 +994,41 @@
       <c r="C29" s="4"/>
       <c r="D29" s="10"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>24</v>
       </c>
       <c r="B30" s="4">
         <v>0.1</v>
       </c>
-      <c r="C30" s="4"/>
+      <c r="C30" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D30" s="10">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="4">
         <v>0.1</v>
       </c>
-      <c r="C31" s="4"/>
+      <c r="C31" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D31" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>26</v>
       </c>
@@ -978,7 +1040,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>21</v>
       </c>
@@ -990,7 +1052,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>22</v>
       </c>
@@ -1002,7 +1064,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>23</v>
       </c>
@@ -1014,19 +1076,24 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B36" s="4">
         <v>0.1</v>
       </c>
-      <c r="C36" s="4"/>
+      <c r="C36" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D36" s="10">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E36" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>22</v>
       </c>
@@ -1038,7 +1105,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
@@ -1049,7 +1116,7 @@
       </c>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>37</v>
       </c>
@@ -1061,7 +1128,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>39</v>
       </c>
@@ -1073,7 +1140,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>31</v>
       </c>
@@ -1085,7 +1152,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>32</v>
       </c>
@@ -1093,43 +1160,58 @@
       <c r="C42" s="4"/>
       <c r="D42" s="10"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>36</v>
       </c>
       <c r="B43" s="4">
         <v>0.1</v>
       </c>
-      <c r="C43" s="4"/>
+      <c r="C43" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D43" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="11" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="4">
         <v>0.1</v>
       </c>
-      <c r="C44" s="4"/>
+      <c r="C44" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D44" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E44" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
         <v>33</v>
       </c>
       <c r="B45" s="4">
         <v>0.1</v>
       </c>
-      <c r="C45" s="4"/>
+      <c r="C45" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="D45" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E45" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="11" t="s">
         <v>34</v>
       </c>
@@ -1141,7 +1223,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
@@ -1152,7 +1234,7 @@
       </c>
       <c r="D47" s="6"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
         <v>41</v>
       </c>
@@ -1187,7 +1269,7 @@
       </c>
       <c r="D50" s="9">
         <f>SUM(D3:D49)</f>
-        <v>5.0000000000000018</v>
+        <v>4.4000000000000021</v>
       </c>
     </row>
   </sheetData>
